--- a/astro-site/public/dl/catering-checklist-templates/03-catering-event-manager-checklist.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/03-catering-event-manager-checklist.xlsx
@@ -1160,7 +1160,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>During the event</t>
+          <t>During the Event</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Control service timing: starter, mains, dessert, coffee</t>
+          <t>Control service timing: appetizers, entrées, dessert, coffee</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>After event</t>
+          <t>After the Event</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G47">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>This quarter's new hires: Form I-9 and W-4 for each new event employee, and the time-clock records filed</t>
+          <t>This quarter's new hires: check each new event employee has Form I-9 (completed by their 3rd business day) and W-4 on file, and the time-clock records filed</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2333,7 +2333,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G34">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
